--- a/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T17:12:06+00:00</t>
+    <t>2024-02-08T17:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T17:26:13+00:00</t>
+    <t>2024-02-12T10:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T10:58:18+00:00</t>
+    <t>2024-02-12T12:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/ig/nr-update-nir/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:41:31+00:00</t>
+    <t>2024-02-12T13:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
